--- a/data-manipulation-scripts/sheets-cleanup/sheets/ROLAMENTO AGULHA_.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/ROLAMENTO AGULHA_.xlsx
@@ -399,7 +399,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="4">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="D3" s="4">
         <v>25.0</v>
